--- a/bench/results/jmeter_S4a_analysis.xlsx
+++ b/bench/results/jmeter_S4a_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81247102-2DF3-415A-A551-D70895054E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5EF369-A6DC-46B0-BBFE-0DE2D1CACED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="7080" windowWidth="19410" windowHeight="10545" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3480" windowWidth="38640" windowHeight="21120" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/bench/results/jmeter_S4a_analysis.xlsx
+++ b/bench/results/jmeter_S4a_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5EF369-A6DC-46B0-BBFE-0DE2D1CACED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7155DAB0-FEBF-4357-926F-48463099159A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3480" windowWidth="38640" windowHeight="21120" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -246,7 +246,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" baseline="0"/>
-              <a:t>(Scenario 3)</a:t>
+              <a:t>(Scenario 4a)</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB"/>
           </a:p>
@@ -997,7 +997,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-GB"/>
-              <a:t>(Scenario 3)</a:t>
+              <a:t>(Scenario 4a)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1751,7 +1751,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t>(Scenario 3)</a:t>
+              <a:t>(Scenario 4a)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2728,7 +2728,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" baseline="0"/>
-              <a:t> 3)</a:t>
+              <a:t> 4a)</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB"/>
           </a:p>
@@ -3478,7 +3478,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t>) (Scenario 3)</a:t>
+              <a:t>) (Scenario 4a)</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3585,16 +3585,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>39.950000000000003</c:v>
+                  <c:v>42.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>41.05</c:v>
+                  <c:v>44.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41.05</c:v>
+                  <c:v>47.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41.35</c:v>
+                  <c:v>51.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3672,16 +3672,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>35.5</c:v>
+                  <c:v>36.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>35.5</c:v>
+                  <c:v>37.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.5</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>35.5</c:v>
+                  <c:v>38.799999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3759,16 +3759,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>38</c:v>
+                  <c:v>40.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.85</c:v>
+                  <c:v>42.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40.85</c:v>
+                  <c:v>45.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40.85</c:v>
+                  <c:v>48.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3846,16 +3846,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>37.75</c:v>
+                  <c:v>38.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.75</c:v>
+                  <c:v>40.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.75</c:v>
+                  <c:v>42.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.75</c:v>
+                  <c:v>44.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8074,16 +8074,16 @@
         <v>100</v>
       </c>
       <c r="P22" s="6">
-        <v>39.950000000000003</v>
+        <v>42.1</v>
       </c>
       <c r="Q22" s="6">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="R22" s="6">
-        <v>38</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="S22" s="6">
-        <v>37.75</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8106,16 +8106,16 @@
         <v>1000</v>
       </c>
       <c r="P23" s="6">
-        <v>41.05</v>
+        <v>44.5</v>
       </c>
       <c r="Q23" s="6">
-        <v>35.5</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="R23" s="6">
-        <v>40.85</v>
+        <v>42.8</v>
       </c>
       <c r="S23" s="6">
-        <v>37.75</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8138,16 +8138,16 @@
         <v>5000</v>
       </c>
       <c r="P24" s="6">
-        <v>41.05</v>
+        <v>47.8</v>
       </c>
       <c r="Q24" s="6">
-        <v>35.5</v>
+        <v>38</v>
       </c>
       <c r="R24" s="6">
-        <v>40.85</v>
+        <v>45.6</v>
       </c>
       <c r="S24" s="6">
-        <v>37.75</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8170,16 +8170,16 @@
         <v>10000</v>
       </c>
       <c r="P25" s="6">
-        <v>41.35</v>
+        <v>51.2</v>
       </c>
       <c r="Q25" s="6">
-        <v>35.5</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="R25" s="6">
-        <v>40.85</v>
+        <v>48.9</v>
       </c>
       <c r="S25" s="6">
-        <v>37.75</v>
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
